--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1156,6 +1156,357 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130293300</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gröntuvmyran, Gröntuvmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>489073</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6689056</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska högst upp och äldre längre ner.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130292121</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gröntuvmyran, Gröntuvmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>489044</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6688964</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130293417</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gröntuvmyran, Gröntuvmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>489008</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6689034</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1508,6 +1508,638 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130326350</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79275</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>967</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Varglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Letharia vulpina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hökmyrbrännan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>489092</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6688866</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>skvattramtallmosse</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130326364</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78937</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hökmyrbrännan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>489092</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6688866</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>skvattramtallmosse</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130326470</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79799</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hökmyrbrännan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>489065</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6688857</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Lingontallskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # gammal rotvälta # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130326355</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79204</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hökmyrbrännan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>489092</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6688866</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>skvattramtallmosse</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130330612</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hökmyrbrännan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>489160</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6688904</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -1276,7 +1276,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130292121</v>
+        <v>130293417</v>
       </c>
       <c r="B7" t="n">
         <v>57826</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489044</v>
+        <v>489008</v>
       </c>
       <c r="R7" t="n">
-        <v>6688964</v>
+        <v>6689034</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130293417</v>
+        <v>130292121</v>
       </c>
       <c r="B8" t="n">
         <v>57826</v>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489008</v>
+        <v>489044</v>
       </c>
       <c r="R8" t="n">
-        <v>6689034</v>
+        <v>6688964</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -1276,7 +1276,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130293417</v>
+        <v>130292121</v>
       </c>
       <c r="B7" t="n">
         <v>57826</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489008</v>
+        <v>489044</v>
       </c>
       <c r="R7" t="n">
-        <v>6689034</v>
+        <v>6688964</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130292121</v>
+        <v>130293417</v>
       </c>
       <c r="B8" t="n">
         <v>57826</v>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489044</v>
+        <v>489008</v>
       </c>
       <c r="R8" t="n">
-        <v>6688964</v>
+        <v>6689034</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -1513,7 +1513,7 @@
         <v>130326350</v>
       </c>
       <c r="B9" t="n">
-        <v>79275</v>
+        <v>79278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130326364</v>
+        <v>130326470</v>
       </c>
       <c r="B10" t="n">
-        <v>78937</v>
+        <v>79802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,21 +1660,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489092</v>
+        <v>489065</v>
       </c>
       <c r="R10" t="n">
-        <v>6688866</v>
+        <v>6688857</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1737,12 +1737,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>skvattramtallmosse</t>
+          <t>Lingontallskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1757,12 +1752,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # gammal rotvälta # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130326470</v>
+        <v>130326364</v>
       </c>
       <c r="B11" t="n">
-        <v>79799</v>
+        <v>78940</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,21 +1786,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1818,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489065</v>
+        <v>489092</v>
       </c>
       <c r="R11" t="n">
-        <v>6688857</v>
+        <v>6688866</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1868,7 +1863,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Lingontallskog</t>
+          <t>Tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>skvattramtallmosse</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # gammal rotvälta # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1909,7 +1909,7 @@
         <v>130326355</v>
       </c>
       <c r="B12" t="n">
-        <v>79204</v>
+        <v>79207</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>130293300</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>130293417</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>130292121</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>130326350</v>
       </c>
       <c r="B9" t="n">
-        <v>79278</v>
+        <v>79304</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130326470</v>
+        <v>130326364</v>
       </c>
       <c r="B10" t="n">
-        <v>79802</v>
+        <v>78966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,21 +1660,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489065</v>
+        <v>489092</v>
       </c>
       <c r="R10" t="n">
-        <v>6688857</v>
+        <v>6688866</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1737,7 +1737,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Lingontallskog</t>
+          <t>Tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>skvattramtallmosse</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1752,12 +1757,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # gammal rotvälta # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130326364</v>
+        <v>130326470</v>
       </c>
       <c r="B11" t="n">
-        <v>78940</v>
+        <v>79828</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,21 +1791,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1813,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489092</v>
+        <v>489065</v>
       </c>
       <c r="R11" t="n">
-        <v>6688866</v>
+        <v>6688857</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1863,12 +1868,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>skvattramtallmosse</t>
+          <t>Lingontallskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # gammal rotvälta # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1909,7 +1909,7 @@
         <v>130326355</v>
       </c>
       <c r="B12" t="n">
-        <v>79207</v>
+        <v>79233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>130330612</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -1276,7 +1276,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130293417</v>
+        <v>130292121</v>
       </c>
       <c r="B7" t="n">
         <v>57852</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489008</v>
+        <v>489044</v>
       </c>
       <c r="R7" t="n">
-        <v>6689034</v>
+        <v>6688964</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130292121</v>
+        <v>130293417</v>
       </c>
       <c r="B8" t="n">
         <v>57852</v>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489044</v>
+        <v>489008</v>
       </c>
       <c r="R8" t="n">
-        <v>6688964</v>
+        <v>6689034</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -1276,7 +1276,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130292121</v>
+        <v>130293417</v>
       </c>
       <c r="B7" t="n">
         <v>57852</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489044</v>
+        <v>489008</v>
       </c>
       <c r="R7" t="n">
-        <v>6688964</v>
+        <v>6689034</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130293417</v>
+        <v>130292121</v>
       </c>
       <c r="B8" t="n">
         <v>57852</v>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489008</v>
+        <v>489044</v>
       </c>
       <c r="R8" t="n">
-        <v>6689034</v>
+        <v>6688964</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1649,10 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130326364</v>
+        <v>130326470</v>
       </c>
       <c r="B10" t="n">
-        <v>78966</v>
+        <v>79828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,21 +1660,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489092</v>
+        <v>489065</v>
       </c>
       <c r="R10" t="n">
-        <v>6688866</v>
+        <v>6688857</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1737,12 +1737,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>skvattramtallmosse</t>
+          <t>Lingontallskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1757,12 +1752,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # gammal rotvälta # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130326470</v>
+        <v>130326364</v>
       </c>
       <c r="B11" t="n">
-        <v>79828</v>
+        <v>78966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,21 +1786,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1818,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489065</v>
+        <v>489092</v>
       </c>
       <c r="R11" t="n">
-        <v>6688857</v>
+        <v>6688866</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1868,7 +1863,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Lingontallskog</t>
+          <t>Tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>skvattramtallmosse</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # gammal rotvälta # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>130293300</v>
       </c>
       <c r="B6" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>130293417</v>
       </c>
       <c r="B7" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>130292121</v>
       </c>
       <c r="B8" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>130326350</v>
       </c>
       <c r="B9" t="n">
-        <v>79304</v>
+        <v>79306</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130326470</v>
+        <v>130326364</v>
       </c>
       <c r="B10" t="n">
-        <v>79828</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,21 +1660,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489065</v>
+        <v>489092</v>
       </c>
       <c r="R10" t="n">
-        <v>6688857</v>
+        <v>6688866</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1737,7 +1737,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Lingontallskog</t>
+          <t>Tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>skvattramtallmosse</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1752,12 +1757,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # gammal rotvälta # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130326364</v>
+        <v>130326470</v>
       </c>
       <c r="B11" t="n">
-        <v>78966</v>
+        <v>79830</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,21 +1791,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1813,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489092</v>
+        <v>489065</v>
       </c>
       <c r="R11" t="n">
-        <v>6688866</v>
+        <v>6688857</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1863,12 +1868,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>skvattramtallmosse</t>
+          <t>Lingontallskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # gammal rotvälta # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Alec Bailey</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1909,7 +1909,7 @@
         <v>130326355</v>
       </c>
       <c r="B12" t="n">
-        <v>79233</v>
+        <v>79235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>130330612</v>
       </c>
       <c r="B13" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Janolof Hermansson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -1649,10 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130326364</v>
+        <v>130326470</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>79830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,21 +1660,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489092</v>
+        <v>489065</v>
       </c>
       <c r="R10" t="n">
-        <v>6688866</v>
+        <v>6688857</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1737,12 +1737,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>skvattramtallmosse</t>
+          <t>Lingontallskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1757,12 +1752,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # gammal rotvälta # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130326470</v>
+        <v>130326364</v>
       </c>
       <c r="B11" t="n">
-        <v>79830</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,21 +1786,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1818,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489065</v>
+        <v>489092</v>
       </c>
       <c r="R11" t="n">
-        <v>6688857</v>
+        <v>6688866</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1868,7 +1863,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Lingontallskog</t>
+          <t>Tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>skvattramtallmosse</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # gammal rotvälta # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -1649,10 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130326470</v>
+        <v>130326364</v>
       </c>
       <c r="B10" t="n">
-        <v>79830</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,21 +1660,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489065</v>
+        <v>489092</v>
       </c>
       <c r="R10" t="n">
-        <v>6688857</v>
+        <v>6688866</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1737,7 +1737,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Lingontallskog</t>
+          <t>Tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>skvattramtallmosse</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1752,12 +1757,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # gammal rotvälta # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130326364</v>
+        <v>130326470</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>79830</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,21 +1791,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1813,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489092</v>
+        <v>489065</v>
       </c>
       <c r="R11" t="n">
-        <v>6688866</v>
+        <v>6688857</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1863,12 +1868,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>skvattramtallmosse</t>
+          <t>Lingontallskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # kelo # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # gammal rotvälta # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>130293300</v>
       </c>
       <c r="B6" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>130293417</v>
       </c>
       <c r="B7" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>130292121</v>
       </c>
       <c r="B8" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>130326350</v>
       </c>
       <c r="B9" t="n">
-        <v>79306</v>
+        <v>79314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>130326364</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>130326470</v>
       </c>
       <c r="B11" t="n">
-        <v>79830</v>
+        <v>79838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>130326355</v>
       </c>
       <c r="B12" t="n">
-        <v>79235</v>
+        <v>79243</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>130330612</v>
       </c>
       <c r="B13" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>130293300</v>
       </c>
       <c r="B6" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>130293417</v>
       </c>
       <c r="B7" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>130292121</v>
       </c>
       <c r="B8" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>130326350</v>
       </c>
       <c r="B9" t="n">
-        <v>79314</v>
+        <v>79315</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>130326364</v>
       </c>
       <c r="B10" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>130326470</v>
       </c>
       <c r="B11" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>130326355</v>
       </c>
       <c r="B12" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>130330612</v>
       </c>
       <c r="B13" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42712-2025 artfynd.xlsx
+++ b/artfynd/A 42712-2025 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>130293300</v>
       </c>
       <c r="B6" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>130293417</v>
       </c>
       <c r="B7" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>130292121</v>
       </c>
       <c r="B8" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>130326350</v>
       </c>
       <c r="B9" t="n">
-        <v>79315</v>
+        <v>79316</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>130326364</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>130326470</v>
       </c>
       <c r="B11" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Alec Bailey</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1909,7 +1909,7 @@
         <v>130326355</v>
       </c>
       <c r="B12" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>130330612</v>
       </c>
       <c r="B13" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
